--- a/InputData/trans/AVL/cn - Avg Vehicle Lifetime.xlsx
+++ b/InputData/trans/AVL/cn - Avg Vehicle Lifetime.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\EPS-trans\伊皮埃斯\AVL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zhlxl\Desktop\EPS\eps-china2019-smart-trans\InputData\trans\AVL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8457924-2AE3-4138-BD8B-6C10778E4623}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B877504-FB37-43AC-B4BE-4DF7923D6ACB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-109" yWindow="-109" windowWidth="26301" windowHeight="14169" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="9" r:id="rId1"/>
@@ -1435,34 +1435,34 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="5" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="19" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="17" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="17" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="17" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="1" fontId="14" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="19" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="17" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="17" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="17" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="20">
     <cellStyle name="Body: normal cell" xfId="14" xr:uid="{00000000-0005-0000-0000-00003C000000}"/>
@@ -2294,23 +2294,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C98"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.9" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="2" max="2" width="132.21875" customWidth="1"/>
-    <col min="3" max="3" width="96.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="132.25" customWidth="1"/>
+    <col min="3" max="3" width="96.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A1" s="37" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.15">
       <c r="C2" s="79" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A3" s="37" t="s">
         <v>1</v>
       </c>
@@ -2318,196 +2318,196 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.15">
       <c r="B4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.15">
       <c r="B5" s="5">
         <v>2020</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.15">
       <c r="B6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.15">
       <c r="B7" s="74" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.15">
       <c r="B8" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.15">
       <c r="B10" s="75" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.15">
       <c r="B11" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.15">
       <c r="B12" s="5">
         <v>2013</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.15">
       <c r="B13" s="79" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.15">
       <c r="B14" s="74" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.15">
       <c r="B15" s="5" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B17" s="75" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B18" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B19" s="5">
         <v>2020</v>
       </c>
     </row>
-    <row r="20" spans="2:3" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:3" ht="16.3" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>12</v>
       </c>
       <c r="C20" s="76"/>
     </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B21" s="74" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B22" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B24" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B25" s="5" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B27" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B28" s="5">
         <v>2020</v>
       </c>
     </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B29" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B30" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="32" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B32" s="75" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B33" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B34" s="5">
         <v>2020</v>
       </c>
     </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B35" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="36" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B36" s="74" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B37" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="39" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B39" s="75" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="40" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B40" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="41" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B41" s="5">
         <v>2013</v>
       </c>
     </row>
-    <row r="42" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B42" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="43" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B43" s="74" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="44" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B44" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="45" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B45" s="79" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="46" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B46" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="47" spans="2:3" ht="15" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:3" ht="15.65" x14ac:dyDescent="0.25">
       <c r="C47" s="77"/>
     </row>
-    <row r="48" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B48" s="6" t="s">
         <v>23</v>
       </c>
@@ -2515,7 +2515,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="49" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B49" t="s">
         <v>24</v>
       </c>
@@ -2523,12 +2523,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="50" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B50" s="5">
         <v>2020</v>
       </c>
     </row>
-    <row r="51" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B51" s="79" t="s">
         <v>160</v>
       </c>
@@ -2536,20 +2536,20 @@
         <v>163</v>
       </c>
     </row>
-    <row r="52" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B52" s="74" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="53" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B53" s="37"/>
     </row>
-    <row r="54" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B54" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="55" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B55" s="5">
         <v>2019</v>
       </c>
@@ -2557,27 +2557,27 @@
         <v>165</v>
       </c>
     </row>
-    <row r="56" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B56" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="57" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B57" s="78" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="58" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B58" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="60" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B60" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="61" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B61" s="5">
         <v>2019</v>
       </c>
@@ -2585,22 +2585,22 @@
         <v>167</v>
       </c>
     </row>
-    <row r="62" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B62" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="63" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B63" s="74" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="64" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B64" s="79" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="65" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B65" t="s">
         <v>168</v>
       </c>
@@ -2608,13 +2608,13 @@
         <v>170</v>
       </c>
     </row>
-    <row r="66" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B66" s="79" t="s">
         <v>172</v>
       </c>
       <c r="C66" s="79"/>
     </row>
-    <row r="67" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B67" t="s">
         <v>171</v>
       </c>
@@ -2622,37 +2622,37 @@
         <v>173</v>
       </c>
     </row>
-    <row r="69" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B69" s="6" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="70" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B70" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="71" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B71" s="5">
         <v>2020</v>
       </c>
     </row>
-    <row r="72" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="72" spans="2:3" ht="17.7" x14ac:dyDescent="0.35">
       <c r="B72" s="80" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="73" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B73" s="74" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="74" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B74" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="76" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B76" t="s">
         <v>33</v>
       </c>
@@ -2660,7 +2660,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="77" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B77" s="5">
         <v>2013</v>
       </c>
@@ -2668,77 +2668,77 @@
         <v>35</v>
       </c>
     </row>
-    <row r="78" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B78" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="79" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B79" s="74" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="80" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B80" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.15">
       <c r="B83" s="75" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.15">
       <c r="B84" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.15">
       <c r="B85" s="5">
         <v>2020</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.15">
       <c r="B86" s="79" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.15">
       <c r="B87" s="74" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.15">
       <c r="B88" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A90" s="37" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A91" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A93" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A94" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A96" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A98" t="s">
         <v>43</v>
       </c>
@@ -2764,32 +2764,32 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A2:I99"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.9" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="31.77734375" customWidth="1"/>
+    <col min="1" max="1" width="31.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.15">
       <c r="I27" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A30" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A56" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A57" s="79" t="s">
         <v>183</v>
       </c>
@@ -2797,32 +2797,32 @@
         <v>184</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A81" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A82" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A83" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A84" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A88" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A99" t="s">
         <v>53</v>
       </c>
@@ -2840,70 +2840,70 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:BB61"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="12.9" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="19.44140625" customWidth="1"/>
-    <col min="2" max="27" width="7.77734375" customWidth="1"/>
-    <col min="28" max="28" width="7.109375" customWidth="1"/>
+    <col min="1" max="1" width="19.5" customWidth="1"/>
+    <col min="2" max="27" width="7.75" customWidth="1"/>
+    <col min="28" max="28" width="7.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="81" t="s">
+    <row r="1" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="85" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="81"/>
-      <c r="C1" s="81"/>
-      <c r="D1" s="81"/>
-      <c r="E1" s="81"/>
-      <c r="F1" s="81"/>
-      <c r="G1" s="81"/>
-      <c r="H1" s="81"/>
-      <c r="I1" s="81"/>
-      <c r="J1" s="81"/>
-      <c r="K1" s="81"/>
-      <c r="L1" s="81"/>
-      <c r="M1" s="81"/>
-      <c r="N1" s="81"/>
-      <c r="O1" s="81"/>
-      <c r="P1" s="81"/>
-      <c r="Q1" s="81"/>
-      <c r="R1" s="81"/>
-      <c r="S1" s="81"/>
-      <c r="T1" s="81"/>
-      <c r="U1" s="81"/>
-      <c r="V1" s="81"/>
-      <c r="W1" s="81"/>
-      <c r="X1" s="81"/>
-      <c r="Y1" s="81"/>
-      <c r="Z1" s="81"/>
-      <c r="AA1" s="81"/>
-      <c r="AB1" s="81"/>
-      <c r="AC1" s="82"/>
-      <c r="AD1" s="82"/>
-      <c r="AE1" s="82"/>
-      <c r="AF1" s="82"/>
-      <c r="AG1" s="82"/>
-      <c r="AH1" s="82"/>
-      <c r="AI1" s="82"/>
-      <c r="AJ1" s="82"/>
-      <c r="AK1" s="82"/>
-      <c r="AL1" s="82"/>
-      <c r="AM1" s="82"/>
-      <c r="AN1" s="82"/>
-      <c r="AO1" s="82"/>
-      <c r="AP1" s="82"/>
-      <c r="AQ1" s="82"/>
-      <c r="AR1" s="82"/>
-      <c r="AS1" s="82"/>
-      <c r="AT1" s="82"/>
-      <c r="AU1" s="82"/>
-      <c r="AV1" s="82"/>
-      <c r="AW1" s="82"/>
-      <c r="AX1" s="82"/>
-      <c r="AY1" s="82"/>
-      <c r="AZ1" s="82"/>
-      <c r="BA1" s="82"/>
-      <c r="BB1" s="82"/>
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="85"/>
+      <c r="H1" s="85"/>
+      <c r="I1" s="85"/>
+      <c r="J1" s="85"/>
+      <c r="K1" s="85"/>
+      <c r="L1" s="85"/>
+      <c r="M1" s="85"/>
+      <c r="N1" s="85"/>
+      <c r="O1" s="85"/>
+      <c r="P1" s="85"/>
+      <c r="Q1" s="85"/>
+      <c r="R1" s="85"/>
+      <c r="S1" s="85"/>
+      <c r="T1" s="85"/>
+      <c r="U1" s="85"/>
+      <c r="V1" s="85"/>
+      <c r="W1" s="85"/>
+      <c r="X1" s="85"/>
+      <c r="Y1" s="85"/>
+      <c r="Z1" s="85"/>
+      <c r="AA1" s="85"/>
+      <c r="AB1" s="85"/>
+      <c r="AC1" s="86"/>
+      <c r="AD1" s="86"/>
+      <c r="AE1" s="86"/>
+      <c r="AF1" s="86"/>
+      <c r="AG1" s="86"/>
+      <c r="AH1" s="86"/>
+      <c r="AI1" s="86"/>
+      <c r="AJ1" s="86"/>
+      <c r="AK1" s="86"/>
+      <c r="AL1" s="86"/>
+      <c r="AM1" s="86"/>
+      <c r="AN1" s="86"/>
+      <c r="AO1" s="86"/>
+      <c r="AP1" s="86"/>
+      <c r="AQ1" s="86"/>
+      <c r="AR1" s="86"/>
+      <c r="AS1" s="86"/>
+      <c r="AT1" s="86"/>
+      <c r="AU1" s="86"/>
+      <c r="AV1" s="86"/>
+      <c r="AW1" s="86"/>
+      <c r="AX1" s="86"/>
+      <c r="AY1" s="86"/>
+      <c r="AZ1" s="86"/>
+      <c r="BA1" s="86"/>
+      <c r="BB1" s="86"/>
     </row>
     <row r="2" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="49"/>
@@ -4925,220 +4925,220 @@
       <c r="BA20" s="61"/>
       <c r="BB20" s="61"/>
     </row>
-    <row r="21" spans="1:54" s="48" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="83" t="s">
+    <row r="21" spans="1:54" s="48" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="87" t="s">
         <v>64</v>
       </c>
-      <c r="B21" s="83"/>
-      <c r="C21" s="83"/>
-      <c r="D21" s="83"/>
-      <c r="E21" s="83"/>
-      <c r="F21" s="83"/>
-      <c r="G21" s="83"/>
-      <c r="H21" s="83"/>
-      <c r="I21" s="83"/>
-      <c r="J21" s="83"/>
-      <c r="K21" s="83"/>
-      <c r="L21" s="83"/>
-      <c r="M21" s="83"/>
-      <c r="N21" s="83"/>
-      <c r="O21" s="83"/>
-      <c r="P21" s="83"/>
-      <c r="Q21" s="83"/>
-    </row>
-    <row r="22" spans="1:54" s="48" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="84"/>
-      <c r="B22" s="84"/>
-      <c r="C22" s="84"/>
-      <c r="D22" s="84"/>
-      <c r="E22" s="84"/>
-      <c r="F22" s="84"/>
-      <c r="G22" s="84"/>
-      <c r="H22" s="84"/>
-      <c r="I22" s="84"/>
-      <c r="J22" s="84"/>
-      <c r="K22" s="84"/>
-      <c r="L22" s="84"/>
-      <c r="M22" s="84"/>
-      <c r="N22" s="84"/>
-      <c r="O22" s="84"/>
-      <c r="P22" s="84"/>
-      <c r="Q22" s="84"/>
-    </row>
-    <row r="23" spans="1:54" s="48" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="84" t="s">
+      <c r="B21" s="87"/>
+      <c r="C21" s="87"/>
+      <c r="D21" s="87"/>
+      <c r="E21" s="87"/>
+      <c r="F21" s="87"/>
+      <c r="G21" s="87"/>
+      <c r="H21" s="87"/>
+      <c r="I21" s="87"/>
+      <c r="J21" s="87"/>
+      <c r="K21" s="87"/>
+      <c r="L21" s="87"/>
+      <c r="M21" s="87"/>
+      <c r="N21" s="87"/>
+      <c r="O21" s="87"/>
+      <c r="P21" s="87"/>
+      <c r="Q21" s="87"/>
+    </row>
+    <row r="22" spans="1:54" s="48" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="88"/>
+      <c r="B22" s="88"/>
+      <c r="C22" s="88"/>
+      <c r="D22" s="88"/>
+      <c r="E22" s="88"/>
+      <c r="F22" s="88"/>
+      <c r="G22" s="88"/>
+      <c r="H22" s="88"/>
+      <c r="I22" s="88"/>
+      <c r="J22" s="88"/>
+      <c r="K22" s="88"/>
+      <c r="L22" s="88"/>
+      <c r="M22" s="88"/>
+      <c r="N22" s="88"/>
+      <c r="O22" s="88"/>
+      <c r="P22" s="88"/>
+      <c r="Q22" s="88"/>
+    </row>
+    <row r="23" spans="1:54" s="48" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="88" t="s">
         <v>65</v>
       </c>
-      <c r="B23" s="84"/>
-      <c r="C23" s="84"/>
-      <c r="D23" s="84"/>
-      <c r="E23" s="84"/>
-      <c r="F23" s="84"/>
-      <c r="G23" s="84"/>
-      <c r="H23" s="84"/>
-      <c r="I23" s="84"/>
-      <c r="J23" s="84"/>
-      <c r="K23" s="84"/>
-      <c r="L23" s="84"/>
-      <c r="M23" s="84"/>
-      <c r="N23" s="84"/>
-      <c r="O23" s="84"/>
-      <c r="P23" s="84"/>
-      <c r="Q23" s="84"/>
-    </row>
-    <row r="24" spans="1:54" s="48" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="86" t="s">
+      <c r="B23" s="88"/>
+      <c r="C23" s="88"/>
+      <c r="D23" s="88"/>
+      <c r="E23" s="88"/>
+      <c r="F23" s="88"/>
+      <c r="G23" s="88"/>
+      <c r="H23" s="88"/>
+      <c r="I23" s="88"/>
+      <c r="J23" s="88"/>
+      <c r="K23" s="88"/>
+      <c r="L23" s="88"/>
+      <c r="M23" s="88"/>
+      <c r="N23" s="88"/>
+      <c r="O23" s="88"/>
+      <c r="P23" s="88"/>
+      <c r="Q23" s="88"/>
+    </row>
+    <row r="24" spans="1:54" s="48" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="90" t="s">
         <v>66</v>
       </c>
-      <c r="B24" s="86"/>
-      <c r="C24" s="86"/>
-      <c r="D24" s="86"/>
-      <c r="E24" s="86"/>
-      <c r="F24" s="86"/>
-      <c r="G24" s="86"/>
-      <c r="H24" s="86"/>
-      <c r="I24" s="86"/>
-      <c r="J24" s="86"/>
-      <c r="K24" s="86"/>
-      <c r="L24" s="86"/>
-      <c r="M24" s="86"/>
-      <c r="N24" s="86"/>
-      <c r="O24" s="86"/>
-      <c r="P24" s="86"/>
-      <c r="Q24" s="86"/>
-    </row>
-    <row r="25" spans="1:54" s="48" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="86" t="s">
+      <c r="B24" s="90"/>
+      <c r="C24" s="90"/>
+      <c r="D24" s="90"/>
+      <c r="E24" s="90"/>
+      <c r="F24" s="90"/>
+      <c r="G24" s="90"/>
+      <c r="H24" s="90"/>
+      <c r="I24" s="90"/>
+      <c r="J24" s="90"/>
+      <c r="K24" s="90"/>
+      <c r="L24" s="90"/>
+      <c r="M24" s="90"/>
+      <c r="N24" s="90"/>
+      <c r="O24" s="90"/>
+      <c r="P24" s="90"/>
+      <c r="Q24" s="90"/>
+    </row>
+    <row r="25" spans="1:54" s="48" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="90" t="s">
         <v>67</v>
       </c>
-      <c r="B25" s="86"/>
-      <c r="C25" s="86"/>
-      <c r="D25" s="86"/>
-      <c r="E25" s="86"/>
-      <c r="F25" s="86"/>
-      <c r="G25" s="86"/>
-      <c r="H25" s="86"/>
-      <c r="I25" s="86"/>
-      <c r="J25" s="86"/>
-      <c r="K25" s="86"/>
-      <c r="L25" s="86"/>
-      <c r="M25" s="86"/>
-      <c r="N25" s="86"/>
-      <c r="O25" s="86"/>
-      <c r="P25" s="86"/>
-      <c r="Q25" s="86"/>
-    </row>
-    <row r="26" spans="1:54" s="48" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="87" t="s">
+      <c r="B25" s="90"/>
+      <c r="C25" s="90"/>
+      <c r="D25" s="90"/>
+      <c r="E25" s="90"/>
+      <c r="F25" s="90"/>
+      <c r="G25" s="90"/>
+      <c r="H25" s="90"/>
+      <c r="I25" s="90"/>
+      <c r="J25" s="90"/>
+      <c r="K25" s="90"/>
+      <c r="L25" s="90"/>
+      <c r="M25" s="90"/>
+      <c r="N25" s="90"/>
+      <c r="O25" s="90"/>
+      <c r="P25" s="90"/>
+      <c r="Q25" s="90"/>
+    </row>
+    <row r="26" spans="1:54" s="48" customFormat="1" ht="27.7" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="91" t="s">
         <v>68</v>
       </c>
-      <c r="B26" s="87"/>
-      <c r="C26" s="87"/>
-      <c r="D26" s="87"/>
-      <c r="E26" s="87"/>
-      <c r="F26" s="87"/>
-      <c r="G26" s="87"/>
-      <c r="H26" s="87"/>
-      <c r="I26" s="87"/>
-      <c r="J26" s="87"/>
-      <c r="K26" s="87"/>
-      <c r="L26" s="87"/>
-      <c r="M26" s="87"/>
-      <c r="N26" s="87"/>
-      <c r="O26" s="87"/>
-      <c r="P26" s="87"/>
-      <c r="Q26" s="87"/>
-    </row>
-    <row r="27" spans="1:54" s="48" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="87"/>
-      <c r="B27" s="87"/>
-      <c r="C27" s="87"/>
-      <c r="D27" s="87"/>
-      <c r="E27" s="87"/>
-      <c r="F27" s="87"/>
-      <c r="G27" s="87"/>
-      <c r="H27" s="87"/>
-      <c r="I27" s="87"/>
-      <c r="J27" s="87"/>
-      <c r="K27" s="87"/>
-      <c r="L27" s="87"/>
-      <c r="M27" s="87"/>
-      <c r="N27" s="87"/>
-      <c r="O27" s="87"/>
-      <c r="P27" s="87"/>
-      <c r="Q27" s="87"/>
-    </row>
-    <row r="28" spans="1:54" s="48" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="88" t="s">
+      <c r="B26" s="91"/>
+      <c r="C26" s="91"/>
+      <c r="D26" s="91"/>
+      <c r="E26" s="91"/>
+      <c r="F26" s="91"/>
+      <c r="G26" s="91"/>
+      <c r="H26" s="91"/>
+      <c r="I26" s="91"/>
+      <c r="J26" s="91"/>
+      <c r="K26" s="91"/>
+      <c r="L26" s="91"/>
+      <c r="M26" s="91"/>
+      <c r="N26" s="91"/>
+      <c r="O26" s="91"/>
+      <c r="P26" s="91"/>
+      <c r="Q26" s="91"/>
+    </row>
+    <row r="27" spans="1:54" s="48" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="91"/>
+      <c r="B27" s="91"/>
+      <c r="C27" s="91"/>
+      <c r="D27" s="91"/>
+      <c r="E27" s="91"/>
+      <c r="F27" s="91"/>
+      <c r="G27" s="91"/>
+      <c r="H27" s="91"/>
+      <c r="I27" s="91"/>
+      <c r="J27" s="91"/>
+      <c r="K27" s="91"/>
+      <c r="L27" s="91"/>
+      <c r="M27" s="91"/>
+      <c r="N27" s="91"/>
+      <c r="O27" s="91"/>
+      <c r="P27" s="91"/>
+      <c r="Q27" s="91"/>
+    </row>
+    <row r="28" spans="1:54" s="48" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A28" s="92" t="s">
         <v>69</v>
       </c>
-      <c r="B28" s="88"/>
-      <c r="C28" s="88"/>
-      <c r="D28" s="88"/>
-      <c r="E28" s="88"/>
-      <c r="F28" s="88"/>
-      <c r="G28" s="88"/>
-      <c r="H28" s="88"/>
-      <c r="I28" s="88"/>
-      <c r="J28" s="88"/>
-      <c r="K28" s="88"/>
-      <c r="L28" s="88"/>
-      <c r="M28" s="88"/>
-      <c r="N28" s="88"/>
-      <c r="O28" s="88"/>
-      <c r="P28" s="88"/>
-      <c r="Q28" s="88"/>
-    </row>
-    <row r="29" spans="1:54" s="48" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="85" t="s">
+      <c r="B28" s="92"/>
+      <c r="C28" s="92"/>
+      <c r="D28" s="92"/>
+      <c r="E28" s="92"/>
+      <c r="F28" s="92"/>
+      <c r="G28" s="92"/>
+      <c r="H28" s="92"/>
+      <c r="I28" s="92"/>
+      <c r="J28" s="92"/>
+      <c r="K28" s="92"/>
+      <c r="L28" s="92"/>
+      <c r="M28" s="92"/>
+      <c r="N28" s="92"/>
+      <c r="O28" s="92"/>
+      <c r="P28" s="92"/>
+      <c r="Q28" s="92"/>
+    </row>
+    <row r="29" spans="1:54" s="48" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A29" s="89" t="s">
         <v>70</v>
       </c>
-      <c r="B29" s="85"/>
-      <c r="C29" s="85"/>
-      <c r="D29" s="85"/>
-      <c r="E29" s="85"/>
-      <c r="F29" s="85"/>
-      <c r="G29" s="85"/>
-      <c r="H29" s="85"/>
-      <c r="I29" s="85"/>
-      <c r="J29" s="85"/>
-      <c r="K29" s="85"/>
-      <c r="L29" s="85"/>
-      <c r="M29" s="85"/>
-      <c r="N29" s="85"/>
-      <c r="O29" s="85"/>
-      <c r="P29" s="85"/>
-      <c r="Q29" s="85"/>
-    </row>
-    <row r="33" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="34" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="35" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="36" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="37" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="38" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="39" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="40" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="41" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="42" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="43" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="44" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="45" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="46" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="47" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="48" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="49" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="50" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="51" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="52" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="53" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="54" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="55" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="56" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="57" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="58" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="59" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="60" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="61" customFormat="1" x14ac:dyDescent="0.25"/>
+      <c r="B29" s="89"/>
+      <c r="C29" s="89"/>
+      <c r="D29" s="89"/>
+      <c r="E29" s="89"/>
+      <c r="F29" s="89"/>
+      <c r="G29" s="89"/>
+      <c r="H29" s="89"/>
+      <c r="I29" s="89"/>
+      <c r="J29" s="89"/>
+      <c r="K29" s="89"/>
+      <c r="L29" s="89"/>
+      <c r="M29" s="89"/>
+      <c r="N29" s="89"/>
+      <c r="O29" s="89"/>
+      <c r="P29" s="89"/>
+      <c r="Q29" s="89"/>
+    </row>
+    <row r="33" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="34" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="35" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="36" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="37" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="38" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="39" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="40" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="41" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="42" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="43" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="44" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="45" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="46" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="47" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="48" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="49" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="50" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="51" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="52" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="53" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="54" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="55" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="56" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="57" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="58" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="59" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="60" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="61" customFormat="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="A29:Q29"/>
@@ -5161,24 +5161,24 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A2:F61"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.9" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="16.21875" customWidth="1"/>
+    <col min="1" max="1" width="16.25" customWidth="1"/>
     <col min="2" max="2" width="31" customWidth="1"/>
-    <col min="3" max="3" width="30.109375" customWidth="1"/>
-    <col min="4" max="4" width="21.88671875" customWidth="1"/>
-    <col min="5" max="5" width="17.109375" customWidth="1"/>
-    <col min="6" max="6" width="15.21875" customWidth="1"/>
+    <col min="3" max="3" width="30.125" customWidth="1"/>
+    <col min="4" max="4" width="21.875" customWidth="1"/>
+    <col min="5" max="5" width="17.125" customWidth="1"/>
+    <col min="6" max="6" width="15.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A2" s="41" t="s">
         <v>31</v>
       </c>
       <c r="B2" s="41"/>
       <c r="C2" s="41"/>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>71</v>
       </c>
@@ -5189,7 +5189,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="16.3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>74</v>
       </c>
@@ -5200,7 +5200,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.15">
       <c r="B6" t="s">
         <v>76</v>
       </c>
@@ -5208,7 +5208,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.15">
       <c r="B7" t="s">
         <v>77</v>
       </c>
@@ -5216,7 +5216,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.15">
       <c r="B8" t="s">
         <v>78</v>
       </c>
@@ -5224,7 +5224,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.15">
       <c r="B9" t="s">
         <v>79</v>
       </c>
@@ -5232,7 +5232,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="16.3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>80</v>
       </c>
@@ -5243,7 +5243,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.15">
       <c r="B12" t="s">
         <v>76</v>
       </c>
@@ -5251,7 +5251,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.15">
       <c r="B13" t="s">
         <v>77</v>
       </c>
@@ -5259,7 +5259,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.15">
       <c r="B14" t="s">
         <v>78</v>
       </c>
@@ -5267,7 +5267,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.15">
       <c r="B15" t="s">
         <v>79</v>
       </c>
@@ -5275,7 +5275,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="25.85" x14ac:dyDescent="0.15">
       <c r="A17" s="43" t="s">
         <v>81</v>
       </c>
@@ -5287,7 +5287,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A18" s="23"/>
       <c r="B18" s="23" t="s">
         <v>83</v>
@@ -5297,14 +5297,14 @@
         <v>32</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A20" s="41" t="s">
         <v>52</v>
       </c>
       <c r="B20" s="41"/>
       <c r="C20" s="41"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B21" t="s">
         <v>72</v>
       </c>
@@ -5321,7 +5321,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B22" t="s">
         <v>87</v>
       </c>
@@ -5329,12 +5329,12 @@
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A23" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A24" t="s">
         <v>89</v>
       </c>
@@ -5356,7 +5356,7 @@
         <v>0.36127443478260868</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A25" t="s">
         <v>91</v>
       </c>
@@ -5371,7 +5371,7 @@
         <v>7.2556521739131075E-4</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B26" t="s">
         <v>93</v>
       </c>
@@ -5382,7 +5382,7 @@
         <v>0.63800000000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A28" t="s">
         <v>94</v>
       </c>
@@ -5390,7 +5390,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B29" t="s">
         <v>96</v>
       </c>
@@ -5402,7 +5402,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" ht="25.85" x14ac:dyDescent="0.15">
       <c r="A32" s="43" t="s">
         <v>81</v>
       </c>
@@ -5414,7 +5414,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A33" s="23"/>
       <c r="B33" s="23" t="s">
         <v>174</v>
@@ -5424,14 +5424,14 @@
         <v>23</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A35" s="41" t="s">
         <v>99</v>
       </c>
       <c r="B35" s="41"/>
       <c r="C35" s="41"/>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A37" t="s">
         <v>100</v>
       </c>
@@ -5442,7 +5442,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.15">
       <c r="B38" t="s">
         <v>102</v>
       </c>
@@ -5450,7 +5450,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.15">
       <c r="B39" t="s">
         <v>103</v>
       </c>
@@ -5458,7 +5458,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.15">
       <c r="B40" t="s">
         <v>104</v>
       </c>
@@ -5466,7 +5466,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.15">
       <c r="B41" t="s">
         <v>105</v>
       </c>
@@ -5474,7 +5474,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.15">
       <c r="B42" t="s">
         <v>106</v>
       </c>
@@ -5482,7 +5482,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.15">
       <c r="B43" t="s">
         <v>107</v>
       </c>
@@ -5490,7 +5490,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.15">
       <c r="B44" t="s">
         <v>108</v>
       </c>
@@ -5498,7 +5498,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.15">
       <c r="B45" t="s">
         <v>109</v>
       </c>
@@ -5506,7 +5506,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.15">
       <c r="B46" s="79" t="s">
         <v>159</v>
       </c>
@@ -5514,12 +5514,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A47" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.15">
       <c r="B48" s="79" t="s">
         <v>189</v>
       </c>
@@ -5527,7 +5527,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.15">
       <c r="B49" s="79" t="s">
         <v>190</v>
       </c>
@@ -5535,7 +5535,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.15">
       <c r="B52" t="s">
         <v>2</v>
       </c>
@@ -5544,7 +5544,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.15">
       <c r="B53" t="s">
         <v>111</v>
       </c>
@@ -5556,7 +5556,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.15">
       <c r="B54" t="s">
         <v>112</v>
       </c>
@@ -5565,7 +5565,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.15">
       <c r="B55" t="s">
         <v>113</v>
       </c>
@@ -5574,7 +5574,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.15">
       <c r="B56" t="s">
         <v>114</v>
       </c>
@@ -5583,14 +5583,14 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A58" s="41" t="s">
         <v>115</v>
       </c>
       <c r="B58" s="41"/>
       <c r="C58" s="41"/>
     </row>
-    <row r="60" spans="1:4" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" ht="25.85" x14ac:dyDescent="0.15">
       <c r="A60" s="43" t="s">
         <v>81</v>
       </c>
@@ -5602,7 +5602,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.15">
       <c r="B61" s="23" t="s">
         <v>117</v>
       </c>
@@ -5620,17 +5620,17 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E48"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="12.9" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="30.109375" style="2" customWidth="1"/>
-    <col min="2" max="2" width="29.88671875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="25.21875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="22.77734375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="25.109375" style="2" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="2"/>
+    <col min="1" max="1" width="30.125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="29.875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="25.25" style="2" customWidth="1"/>
+    <col min="4" max="4" width="22.75" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.125" style="2" customWidth="1"/>
+    <col min="6" max="16384" width="9.125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A1" s="6" t="s">
         <v>118</v>
       </c>
@@ -5639,7 +5639,7 @@
       <c r="D1" s="7"/>
       <c r="E1" s="7"/>
     </row>
-    <row r="2" spans="1:5" s="4" customFormat="1" ht="72" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" s="4" customFormat="1" ht="64.55" x14ac:dyDescent="0.15">
       <c r="A2" s="4" t="s">
         <v>119</v>
       </c>
@@ -5656,7 +5656,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A3" s="2">
         <v>13</v>
       </c>
@@ -5676,12 +5676,12 @@
         <v>13.378781688359696</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A5" s="12" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" ht="25.85" x14ac:dyDescent="0.15">
       <c r="A6" s="8" t="s">
         <v>125</v>
       </c>
@@ -5696,7 +5696,7 @@
       </c>
       <c r="E6" s="4"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A7" s="9">
         <v>28</v>
       </c>
@@ -5711,7 +5711,7 @@
       </c>
       <c r="E7" s="16"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A10" s="12" t="s">
         <v>19</v>
       </c>
@@ -5720,14 +5720,14 @@
       <c r="D10" s="17"/>
       <c r="E10" s="17"/>
     </row>
-    <row r="11" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A11" s="18" t="s">
         <v>129</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="18"/>
     </row>
-    <row r="12" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A12" s="5" t="s">
         <v>130</v>
       </c>
@@ -5735,7 +5735,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="13" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A13" s="5" t="s">
         <v>132</v>
       </c>
@@ -5743,7 +5743,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="14" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A14" s="5" t="s">
         <v>134</v>
       </c>
@@ -5751,17 +5751,17 @@
         <v>135</v>
       </c>
     </row>
-    <row r="15" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A15" s="21" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="16" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A16" s="22">
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A18" s="12" t="s">
         <v>23</v>
       </c>
@@ -5770,7 +5770,7 @@
       <c r="D18" s="17"/>
       <c r="E18" s="17"/>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A19" s="18" t="s">
         <v>137</v>
       </c>
@@ -5781,7 +5781,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
         <v>140</v>
       </c>
@@ -5792,7 +5792,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
         <v>142</v>
       </c>
@@ -5803,7 +5803,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A22"/>
       <c r="B22" s="23" t="s">
         <v>136</v>
@@ -5812,17 +5812,17 @@
         <v>34</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A23" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A24" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A26" s="12" t="s">
         <v>146</v>
       </c>
@@ -5831,7 +5831,7 @@
       <c r="D26" s="17"/>
       <c r="E26" s="17"/>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A27" s="18" t="s">
         <v>137</v>
       </c>
@@ -5842,7 +5842,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A28" t="s">
         <v>147</v>
       </c>
@@ -5853,7 +5853,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A30" s="12" t="s">
         <v>37</v>
       </c>
@@ -5862,7 +5862,7 @@
       <c r="D30" s="17"/>
       <c r="E30" s="17"/>
     </row>
-    <row r="31" spans="1:5" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" ht="25.85" x14ac:dyDescent="0.15">
       <c r="A31" s="26" t="s">
         <v>149</v>
       </c>
@@ -5879,7 +5879,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A32" s="30">
         <v>1997</v>
       </c>
@@ -5892,7 +5892,7 @@
       <c r="D32" s="5"/>
       <c r="E32" s="5"/>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A33" s="30">
         <v>1998</v>
       </c>
@@ -5911,7 +5911,7 @@
         <v>6.6484424338501588E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A34" s="30">
         <v>1999</v>
       </c>
@@ -5930,7 +5930,7 @@
         <v>2.9143636995467476E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A35" s="30">
         <v>2000</v>
       </c>
@@ -5949,7 +5949,7 @@
         <v>6.8191523924614153E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A36" s="30">
         <v>2001</v>
       </c>
@@ -5968,7 +5968,7 @@
         <v>4.0815360868813244E-3</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A37" s="30">
         <v>2002</v>
       </c>
@@ -5987,7 +5987,7 @@
         <v>0.10769048766665149</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A38" s="30">
         <v>2003</v>
       </c>
@@ -6006,7 +6006,7 @@
         <v>5.9053805049687755E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A39" s="30">
         <v>2004</v>
       </c>
@@ -6025,7 +6025,7 @@
         <v>5.8670234757052138E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A40" s="30">
         <v>2005</v>
       </c>
@@ -6044,7 +6044,7 @@
         <v>6.1781753631599455E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A41" s="30">
         <v>2006</v>
       </c>
@@ -6063,7 +6063,7 @@
         <v>6.5906687839630079E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A42" s="34">
         <v>2007</v>
       </c>
@@ -6082,14 +6082,14 @@
         <v>5.9604038733197397E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A43"/>
       <c r="B43"/>
       <c r="C43"/>
       <c r="D43"/>
       <c r="E43"/>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A44" s="37" t="s">
         <v>154</v>
       </c>
@@ -6097,7 +6097,7 @@
       <c r="C44"/>
       <c r="D44"/>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A45" s="38">
         <f>AVERAGE(E33:E42)</f>
         <v>5.8060812902328285E-2</v>
@@ -6106,13 +6106,13 @@
       <c r="C45"/>
       <c r="D45"/>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A46"/>
       <c r="B46"/>
       <c r="C46"/>
       <c r="D46"/>
     </row>
-    <row r="47" spans="1:5" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" ht="25.85" x14ac:dyDescent="0.15">
       <c r="A47" s="39" t="s">
         <v>155</v>
       </c>
@@ -6120,7 +6120,7 @@
       <c r="C47"/>
       <c r="D47"/>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A48" s="40">
         <f>1/A45</f>
         <v>17.22332068760786</v>
@@ -6144,14 +6144,14 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.9" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="14.5546875" customWidth="1"/>
+    <col min="1" max="1" width="14.5" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="15.5546875" customWidth="1"/>
+    <col min="3" max="3" width="15.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="38.75" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>156</v>
       </c>
@@ -6162,33 +6162,33 @@
         <v>110</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>118</v>
       </c>
-      <c r="B2" s="90">
+      <c r="B2" s="82">
         <f>'China-Data'!C52</f>
         <v>9</v>
       </c>
-      <c r="C2" s="90">
+      <c r="C2" s="82">
         <f>'China-Data'!C54</f>
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>124</v>
       </c>
-      <c r="B3" s="91">
+      <c r="B3" s="83">
         <f>'China-Data'!C53</f>
         <v>15</v>
       </c>
-      <c r="C3" s="92">
+      <c r="C3" s="84">
         <f>'China-Data'!C55</f>
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -6201,7 +6201,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -6214,7 +6214,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>146</v>
       </c>
@@ -6227,7 +6227,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>37</v>
       </c>
@@ -6240,8 +6240,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G10" s="89"/>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G10" s="81"/>
     </row>
   </sheetData>
   <phoneticPr fontId="25" type="noConversion"/>
@@ -6250,15 +6250,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="文档" ma:contentTypeID="0x010100BD1DE36A36CC7845A4126EF01914151E" ma:contentTypeVersion="14" ma:contentTypeDescription="新建文档。" ma:contentTypeScope="" ma:versionID="310835f059701aa681930bc3a1715053">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="2e2398b5-f60e-4ca0-a4ba-6048b5e4e90c" xmlns:ns3="a06c533b-533a-4f75-b7db-110f073002e4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7ba933288dd05553e9ce0f804d4dc608" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -6492,7 +6483,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
@@ -6501,20 +6492,29 @@
 </p:properties>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69C74C53-8EA3-44B3-AFB2-A1D5E33B8CA3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4B20D90-6D19-4981-A049-161A8DCB346F}">
   <ds:schemaRefs/>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4B20D90-6D19-4981-A049-161A8DCB346F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F341FBFC-3852-4B97-8A25-F4DF1503F524}">
   <ds:schemaRefs/>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F341FBFC-3852-4B97-8A25-F4DF1503F524}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69C74C53-8EA3-44B3-AFB2-A1D5E33B8CA3}">
   <ds:schemaRefs/>
 </ds:datastoreItem>
 </file>